--- a/DAT/raw/data_BodyPerception.xlsx
+++ b/DAT/raw/data_BodyPerception.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/delphinehund/Desktop/Stage/Projet 1 Weight Stigma/Pré-manip/V2/code/DAT/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/delphinehund/Desktop/Stage/Pilot_Study-SocBodPer/V2/code/DAT/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64596AE-3C11-D041-93B1-FAD062F79D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/DAT/raw/data_BodyPerception.xlsx
+++ b/DAT/raw/data_BodyPerception.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/delphinehund/Desktop/Stage/Pilot_Study-SocBodPer/V2/code/DAT/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64596AE-3C11-D041-93B1-FAD062F79D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F26C285-2B47-2D43-9702-D4EACE13BA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="1240" windowWidth="27640" windowHeight="16440" xr2:uid="{A566A536-5EC8-E945-9F1D-F732F8E5AE93}"/>
   </bookViews>
@@ -95,9 +95,6 @@
     <t>HALA</t>
   </si>
   <si>
-    <t>21 ans</t>
-  </si>
-  <si>
     <t>Sauveteuse en piscine</t>
   </si>
   <si>
@@ -641,9 +638,6 @@
     <t>CHMA</t>
   </si>
   <si>
-    <t>63 ans</t>
-  </si>
-  <si>
     <t>Retraitée</t>
   </si>
   <si>
@@ -669,6 +663,12 @@
   </si>
   <si>
     <t>professeur des ecoles</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>63</t>
   </si>
 </sst>
 </file>
@@ -1124,355 +1124,355 @@
   <sheetData>
     <row r="1" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="S1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="T1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="U1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="V1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="W1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="X1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="Y1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Z1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="AA1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AC1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AD1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AE1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AF1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="AG1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AH1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="AH1" s="7" t="s">
+      <c r="AI1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AJ1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="AJ1" s="7" t="s">
+      <c r="AK1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="AK1" s="7" t="s">
+      <c r="AL1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="AL1" s="7" t="s">
+      <c r="AM1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="AM1" s="7" t="s">
+      <c r="AN1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="AN1" s="7" t="s">
+      <c r="AO1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="AO1" s="7" t="s">
+      <c r="AP1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="AP1" s="7" t="s">
+      <c r="AQ1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="AQ1" s="7" t="s">
+      <c r="AR1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="AR1" s="7" t="s">
+      <c r="AS1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AS1" s="7" t="s">
+      <c r="AT1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="AT1" s="7" t="s">
+      <c r="AU1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="AU1" s="7" t="s">
+      <c r="AV1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="AV1" s="7" t="s">
+      <c r="AW1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="AW1" s="7" t="s">
+      <c r="AX1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="AX1" s="7" t="s">
+      <c r="AY1" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="AY1" s="7" t="s">
+      <c r="AZ1" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="AZ1" s="7" t="s">
+      <c r="BA1" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="BA1" s="7" t="s">
+      <c r="BB1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="BB1" s="7" t="s">
+      <c r="BC1" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="BC1" s="7" t="s">
+      <c r="BD1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="BD1" s="7" t="s">
+      <c r="BE1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="BE1" s="7" t="s">
+      <c r="BF1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="BF1" s="7" t="s">
+      <c r="BG1" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="BG1" s="7" t="s">
+      <c r="BH1" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="BH1" s="7" t="s">
+      <c r="BI1" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="BI1" s="7" t="s">
+      <c r="BJ1" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="BJ1" s="7" t="s">
+      <c r="BK1" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="BK1" s="7" t="s">
+      <c r="BL1" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="BL1" s="7" t="s">
+      <c r="BM1" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="BM1" s="7" t="s">
+      <c r="BN1" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="BN1" s="7" t="s">
+      <c r="BO1" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="BO1" s="7" t="s">
+      <c r="BP1" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="BP1" s="7" t="s">
+      <c r="BQ1" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="BQ1" s="7" t="s">
+      <c r="BR1" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="BR1" s="7" t="s">
+      <c r="BS1" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="BS1" s="7" t="s">
+      <c r="BT1" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="BT1" s="7" t="s">
+      <c r="BU1" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="BU1" s="7" t="s">
+      <c r="BV1" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="BV1" s="7" t="s">
+      <c r="BW1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="BW1" s="7" t="s">
+      <c r="BX1" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="BX1" s="7" t="s">
+      <c r="BY1" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="BY1" s="7" t="s">
+      <c r="BZ1" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="BZ1" s="7" t="s">
+      <c r="CA1" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="CA1" s="7" t="s">
+      <c r="CB1" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="CB1" s="7" t="s">
+      <c r="CC1" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="CC1" s="7" t="s">
-        <v>101</v>
-      </c>
       <c r="CD1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="CE1" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="CE1" s="7" t="s">
+      <c r="CF1" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="CF1" s="7" t="s">
+      <c r="CG1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="CG1" s="7" t="s">
+      <c r="CH1" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="CH1" s="7" t="s">
+      <c r="CI1" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="CI1" s="7" t="s">
+      <c r="CJ1" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="CJ1" s="7" t="s">
+      <c r="CK1" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="CK1" s="7" t="s">
+      <c r="CL1" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="CL1" s="7" t="s">
+      <c r="CM1" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="CM1" s="7" t="s">
+      <c r="CN1" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="CN1" s="7" t="s">
+      <c r="CO1" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="CO1" s="7" t="s">
+      <c r="CP1" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="CP1" s="7" t="s">
+      <c r="CQ1" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="CQ1" s="7" t="s">
+      <c r="CR1" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="CR1" s="7" t="s">
+      <c r="CS1" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="CS1" s="7" t="s">
+      <c r="CT1" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="CT1" s="7" t="s">
+      <c r="CU1" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="CU1" s="7" t="s">
+      <c r="CV1" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="CV1" s="7" t="s">
+      <c r="CW1" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="CW1" s="7" t="s">
+      <c r="CX1" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="CX1" s="7" t="s">
+      <c r="CY1" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="CY1" s="7" t="s">
+      <c r="CZ1" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="CZ1" s="7" t="s">
+      <c r="DA1" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="DA1" s="7" t="s">
+      <c r="DB1" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="DB1" s="7" t="s">
+      <c r="DC1" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="DC1" s="7" t="s">
+      <c r="DD1" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="DD1" s="7" t="s">
+      <c r="DE1" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="DE1" s="7" t="s">
+      <c r="DF1" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="DF1" s="7" t="s">
+      <c r="DG1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="DG1" s="7" t="s">
+      <c r="DH1" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="DH1" s="7" t="s">
+      <c r="DI1" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="DI1" s="7" t="s">
+      <c r="DJ1" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="DJ1" s="7" t="s">
+      <c r="DK1" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="DK1" s="7" t="s">
+      <c r="DL1" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="DL1" s="7" t="s">
+      <c r="DM1" s="8" t="s">
         <v>136</v>
-      </c>
-      <c r="DM1" s="8" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:117" x14ac:dyDescent="0.2">
@@ -1853,16 +1853,16 @@
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="M3" s="4">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="M3" s="4">
-        <v>1</v>
-      </c>
-      <c r="N3" s="4">
-        <v>1</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="P3" s="4">
         <v>2</v>
@@ -2194,22 +2194,22 @@
         <v>1</v>
       </c>
       <c r="J4" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K4" s="9">
+        <v>1</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="M4" s="9">
+        <v>1</v>
+      </c>
+      <c r="N4" s="9">
+        <v>1</v>
+      </c>
+      <c r="O4" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="K4" s="9">
-        <v>1</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="M4" s="9">
-        <v>1</v>
-      </c>
-      <c r="N4" s="9">
-        <v>1</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="P4" s="9">
         <v>2</v>
@@ -2541,22 +2541,22 @@
         <v>1</v>
       </c>
       <c r="J5" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="K5" s="9">
+        <v>1</v>
+      </c>
+      <c r="L5" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="K5" s="9">
-        <v>1</v>
-      </c>
-      <c r="L5" s="10" t="s">
+      <c r="M5" s="9">
+        <v>1</v>
+      </c>
+      <c r="N5" s="9">
+        <v>1</v>
+      </c>
+      <c r="O5" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="M5" s="9">
-        <v>1</v>
-      </c>
-      <c r="N5" s="9">
-        <v>1</v>
-      </c>
-      <c r="O5" s="10" t="s">
-        <v>143</v>
       </c>
       <c r="P5" s="9">
         <v>2</v>
@@ -2888,22 +2888,22 @@
         <v>1</v>
       </c>
       <c r="J6" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="K6" s="9">
+        <v>1</v>
+      </c>
+      <c r="L6" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="K6" s="9">
-        <v>1</v>
-      </c>
-      <c r="L6" s="10" t="s">
+      <c r="M6" s="9">
+        <v>1</v>
+      </c>
+      <c r="N6" s="9">
+        <v>1</v>
+      </c>
+      <c r="O6" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="M6" s="9">
-        <v>1</v>
-      </c>
-      <c r="N6" s="9">
-        <v>1</v>
-      </c>
-      <c r="O6" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="P6" s="9">
         <v>2</v>
@@ -3235,22 +3235,22 @@
         <v>1</v>
       </c>
       <c r="J7" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K7" s="9">
+        <v>1</v>
+      </c>
+      <c r="L7" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="K7" s="9">
-        <v>1</v>
-      </c>
-      <c r="L7" s="10" t="s">
+      <c r="M7" s="9">
+        <v>2</v>
+      </c>
+      <c r="N7" s="9">
+        <v>1</v>
+      </c>
+      <c r="O7" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="M7" s="9">
-        <v>2</v>
-      </c>
-      <c r="N7" s="9">
-        <v>1</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="P7" s="9">
         <v>1</v>
@@ -3582,13 +3582,13 @@
         <v>1</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K8" s="9">
         <v>1</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M8" s="9">
         <v>2</v>
@@ -3597,7 +3597,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P8" s="9">
         <v>1</v>
@@ -3929,22 +3929,22 @@
         <v>1</v>
       </c>
       <c r="J9" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="K9" s="9">
+        <v>1</v>
+      </c>
+      <c r="L9" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="K9" s="9">
-        <v>1</v>
-      </c>
-      <c r="L9" s="10" t="s">
+      <c r="M9" s="9">
+        <v>1</v>
+      </c>
+      <c r="N9" s="9">
+        <v>1</v>
+      </c>
+      <c r="O9" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="M9" s="9">
-        <v>1</v>
-      </c>
-      <c r="N9" s="9">
-        <v>1</v>
-      </c>
-      <c r="O9" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="P9" s="9">
         <v>1</v>
@@ -4276,14 +4276,14 @@
         <v>1</v>
       </c>
       <c r="J10" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="K10" s="9">
+        <v>1</v>
+      </c>
+      <c r="L10" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="K10" s="9">
-        <v>1</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>155</v>
-      </c>
       <c r="M10" s="9">
         <v>2</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P10" s="9">
         <v>1</v>
@@ -4623,22 +4623,22 @@
         <v>1</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K11" s="9">
         <v>1</v>
       </c>
       <c r="L11" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="M11" s="9">
+        <v>2</v>
+      </c>
+      <c r="N11" s="9">
+        <v>1</v>
+      </c>
+      <c r="O11" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="M11" s="9">
-        <v>2</v>
-      </c>
-      <c r="N11" s="9">
-        <v>1</v>
-      </c>
-      <c r="O11" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="P11" s="9">
         <v>1</v>
@@ -4970,22 +4970,22 @@
         <v>1</v>
       </c>
       <c r="J12" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="K12" s="9">
+        <v>1</v>
+      </c>
+      <c r="L12" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="K12" s="9">
-        <v>1</v>
-      </c>
-      <c r="L12" s="10" t="s">
+      <c r="M12" s="9">
+        <v>2</v>
+      </c>
+      <c r="N12" s="9">
+        <v>1</v>
+      </c>
+      <c r="O12" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="M12" s="9">
-        <v>2</v>
-      </c>
-      <c r="N12" s="9">
-        <v>1</v>
-      </c>
-      <c r="O12" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="P12" s="9">
         <v>1</v>
@@ -5317,22 +5317,22 @@
         <v>1</v>
       </c>
       <c r="J13" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="K13" s="9">
+        <v>1</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="M13" s="9">
+        <v>1</v>
+      </c>
+      <c r="N13" s="9">
+        <v>1</v>
+      </c>
+      <c r="O13" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="K13" s="9">
-        <v>1</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="M13" s="9">
-        <v>1</v>
-      </c>
-      <c r="N13" s="9">
-        <v>1</v>
-      </c>
-      <c r="O13" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="P13" s="9">
         <v>1</v>
@@ -5664,22 +5664,22 @@
         <v>1</v>
       </c>
       <c r="J14" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="K14" s="9">
+        <v>1</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="M14" s="9">
+        <v>1</v>
+      </c>
+      <c r="N14" s="9">
+        <v>1</v>
+      </c>
+      <c r="O14" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="K14" s="9">
-        <v>1</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="M14" s="9">
-        <v>1</v>
-      </c>
-      <c r="N14" s="9">
-        <v>1</v>
-      </c>
-      <c r="O14" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="P14" s="9">
         <v>1</v>
@@ -6011,14 +6011,14 @@
         <v>1</v>
       </c>
       <c r="J15" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="K15" s="9">
+        <v>1</v>
+      </c>
+      <c r="L15" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="K15" s="9">
-        <v>1</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>165</v>
-      </c>
       <c r="M15" s="9">
         <v>1</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>1</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P15" s="9">
         <v>1</v>
@@ -6358,22 +6358,22 @@
         <v>1</v>
       </c>
       <c r="J16" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="K16" s="9">
+        <v>1</v>
+      </c>
+      <c r="L16" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="K16" s="9">
-        <v>1</v>
-      </c>
-      <c r="L16" s="10" t="s">
+      <c r="M16" s="9">
+        <v>2</v>
+      </c>
+      <c r="N16" s="9">
+        <v>1</v>
+      </c>
+      <c r="O16" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="M16" s="9">
-        <v>2</v>
-      </c>
-      <c r="N16" s="9">
-        <v>1</v>
-      </c>
-      <c r="O16" s="10" t="s">
-        <v>168</v>
       </c>
       <c r="P16" s="9">
         <v>1</v>
@@ -6705,22 +6705,22 @@
         <v>1</v>
       </c>
       <c r="J17" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="K17" s="9">
+        <v>1</v>
+      </c>
+      <c r="L17" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="K17" s="9">
-        <v>1</v>
-      </c>
-      <c r="L17" s="10" t="s">
+      <c r="M17" s="9">
+        <v>1</v>
+      </c>
+      <c r="N17" s="9">
+        <v>1</v>
+      </c>
+      <c r="O17" s="10" t="s">
         <v>170</v>
-      </c>
-      <c r="M17" s="9">
-        <v>1</v>
-      </c>
-      <c r="N17" s="9">
-        <v>1</v>
-      </c>
-      <c r="O17" s="10" t="s">
-        <v>171</v>
       </c>
       <c r="P17" s="9">
         <v>1</v>
@@ -7052,13 +7052,13 @@
         <v>1</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K18" s="9">
         <v>1</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M18" s="9">
         <v>3</v>
@@ -7067,7 +7067,7 @@
         <v>1</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P18" s="9">
         <v>1</v>
@@ -7399,22 +7399,22 @@
         <v>1</v>
       </c>
       <c r="J19" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="K19" s="9">
+        <v>1</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="M19" s="9">
+        <v>2</v>
+      </c>
+      <c r="N19" s="9">
+        <v>1</v>
+      </c>
+      <c r="O19" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="K19" s="9">
-        <v>1</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="M19" s="9">
-        <v>2</v>
-      </c>
-      <c r="N19" s="9">
-        <v>1</v>
-      </c>
-      <c r="O19" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="P19" s="9">
         <v>1</v>
@@ -7746,22 +7746,22 @@
         <v>1</v>
       </c>
       <c r="J20" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="K20" s="9">
+        <v>1</v>
+      </c>
+      <c r="L20" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="K20" s="9">
-        <v>1</v>
-      </c>
-      <c r="L20" s="10" t="s">
+      <c r="M20" s="9">
+        <v>2</v>
+      </c>
+      <c r="N20" s="9">
+        <v>1</v>
+      </c>
+      <c r="O20" s="10" t="s">
         <v>176</v>
-      </c>
-      <c r="M20" s="9">
-        <v>2</v>
-      </c>
-      <c r="N20" s="9">
-        <v>1</v>
-      </c>
-      <c r="O20" s="10" t="s">
-        <v>177</v>
       </c>
       <c r="P20" s="9">
         <v>2</v>
@@ -8093,13 +8093,13 @@
         <v>1</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K21" s="9">
         <v>1</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M21" s="9">
         <v>2</v>
@@ -8108,7 +8108,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P21" s="9">
         <v>1</v>
@@ -8440,22 +8440,22 @@
         <v>1</v>
       </c>
       <c r="J22" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="K22" s="9">
+        <v>1</v>
+      </c>
+      <c r="L22" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="K22" s="9">
-        <v>1</v>
-      </c>
-      <c r="L22" s="10" t="s">
+      <c r="M22" s="9">
+        <v>1</v>
+      </c>
+      <c r="N22" s="9">
+        <v>1</v>
+      </c>
+      <c r="O22" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="M22" s="9">
-        <v>1</v>
-      </c>
-      <c r="N22" s="9">
-        <v>1</v>
-      </c>
-      <c r="O22" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="P22" s="9">
         <v>2</v>
@@ -8787,22 +8787,22 @@
         <v>1</v>
       </c>
       <c r="J23" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="K23" s="9">
+        <v>1</v>
+      </c>
+      <c r="L23" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="K23" s="9">
-        <v>1</v>
-      </c>
-      <c r="L23" s="10" t="s">
+      <c r="M23" s="9">
+        <v>2</v>
+      </c>
+      <c r="N23" s="9">
+        <v>1</v>
+      </c>
+      <c r="O23" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="M23" s="9">
-        <v>2</v>
-      </c>
-      <c r="N23" s="9">
-        <v>1</v>
-      </c>
-      <c r="O23" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="P23" s="9">
         <v>1</v>
@@ -9134,22 +9134,22 @@
         <v>1</v>
       </c>
       <c r="J24" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="K24" s="9">
+        <v>1</v>
+      </c>
+      <c r="L24" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="K24" s="9">
-        <v>1</v>
-      </c>
-      <c r="L24" s="10" t="s">
+      <c r="M24" s="9">
+        <v>1</v>
+      </c>
+      <c r="N24" s="9">
+        <v>1</v>
+      </c>
+      <c r="O24" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="M24" s="9">
-        <v>1</v>
-      </c>
-      <c r="N24" s="9">
-        <v>1</v>
-      </c>
-      <c r="O24" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="P24" s="9">
         <v>1</v>
@@ -9481,22 +9481,22 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="K25" s="9">
+        <v>1</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="M25" s="9">
+        <v>2</v>
+      </c>
+      <c r="N25" s="9">
+        <v>1</v>
+      </c>
+      <c r="O25" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="K25" s="9">
-        <v>1</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="M25" s="9">
-        <v>2</v>
-      </c>
-      <c r="N25" s="9">
-        <v>1</v>
-      </c>
-      <c r="O25" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="P25" s="9">
         <v>1</v>
@@ -9828,22 +9828,22 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="K26" s="9">
+        <v>1</v>
+      </c>
+      <c r="L26" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="K26" s="9">
-        <v>1</v>
-      </c>
-      <c r="L26" s="10" t="s">
+      <c r="M26" s="9">
+        <v>1</v>
+      </c>
+      <c r="N26" s="9">
+        <v>1</v>
+      </c>
+      <c r="O26" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="M26" s="9">
-        <v>1</v>
-      </c>
-      <c r="N26" s="9">
-        <v>1</v>
-      </c>
-      <c r="O26" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="P26" s="9">
         <v>1</v>
@@ -10175,22 +10175,22 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="K27" s="9">
+        <v>1</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="M27" s="9">
+        <v>2</v>
+      </c>
+      <c r="N27" s="9">
+        <v>1</v>
+      </c>
+      <c r="O27" s="10" t="s">
         <v>193</v>
-      </c>
-      <c r="K27" s="9">
-        <v>1</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="M27" s="9">
-        <v>2</v>
-      </c>
-      <c r="N27" s="9">
-        <v>1</v>
-      </c>
-      <c r="O27" s="10" t="s">
-        <v>194</v>
       </c>
       <c r="P27" s="9">
         <v>2</v>
@@ -10522,22 +10522,22 @@
         <v>1</v>
       </c>
       <c r="J28" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="K28" s="9">
+        <v>1</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="M28" s="9">
+        <v>1</v>
+      </c>
+      <c r="N28" s="9">
+        <v>1</v>
+      </c>
+      <c r="O28" s="10" t="s">
         <v>195</v>
-      </c>
-      <c r="K28" s="9">
-        <v>1</v>
-      </c>
-      <c r="L28" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="M28" s="9">
-        <v>1</v>
-      </c>
-      <c r="N28" s="9">
-        <v>1</v>
-      </c>
-      <c r="O28" s="10" t="s">
-        <v>196</v>
       </c>
       <c r="P28" s="9">
         <v>1</v>
@@ -10869,22 +10869,22 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="K29" s="9">
+        <v>1</v>
+      </c>
+      <c r="L29" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="K29" s="9">
-        <v>1</v>
-      </c>
-      <c r="L29" s="10" t="s">
+      <c r="M29" s="9">
+        <v>1</v>
+      </c>
+      <c r="N29" s="9">
+        <v>1</v>
+      </c>
+      <c r="O29" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="M29" s="9">
-        <v>1</v>
-      </c>
-      <c r="N29" s="9">
-        <v>1</v>
-      </c>
-      <c r="O29" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="P29" s="9">
         <v>1</v>
@@ -11216,22 +11216,22 @@
         <v>1</v>
       </c>
       <c r="J30" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K30" s="9">
+        <v>1</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="M30" s="9">
+        <v>1</v>
+      </c>
+      <c r="N30" s="9">
+        <v>1</v>
+      </c>
+      <c r="O30" s="10" t="s">
         <v>200</v>
-      </c>
-      <c r="K30" s="9">
-        <v>1</v>
-      </c>
-      <c r="L30" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="M30" s="9">
-        <v>1</v>
-      </c>
-      <c r="N30" s="9">
-        <v>1</v>
-      </c>
-      <c r="O30" s="10" t="s">
-        <v>202</v>
       </c>
       <c r="P30" s="9">
         <v>1</v>
@@ -11563,22 +11563,22 @@
         <v>1</v>
       </c>
       <c r="J31" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="K31" s="9">
+        <v>1</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="M31" s="9">
+        <v>1</v>
+      </c>
+      <c r="N31" s="9">
+        <v>1</v>
+      </c>
+      <c r="O31" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="K31" s="9">
-        <v>1</v>
-      </c>
-      <c r="L31" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="M31" s="9">
-        <v>1</v>
-      </c>
-      <c r="N31" s="9">
-        <v>1</v>
-      </c>
-      <c r="O31" s="10" t="s">
-        <v>205</v>
       </c>
       <c r="P31" s="9">
         <v>2</v>
@@ -11910,13 +11910,13 @@
         <v>1</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K32" s="9">
         <v>1</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M32" s="9">
         <v>1</v>
@@ -11925,7 +11925,7 @@
         <v>1</v>
       </c>
       <c r="O32" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P32" s="9">
         <v>1</v>
@@ -12257,22 +12257,22 @@
         <v>1</v>
       </c>
       <c r="J33" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="K33" s="9">
+        <v>1</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="M33" s="9">
+        <v>1</v>
+      </c>
+      <c r="N33" s="9">
+        <v>1</v>
+      </c>
+      <c r="O33" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="K33" s="9">
-        <v>1</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="M33" s="9">
-        <v>1</v>
-      </c>
-      <c r="N33" s="9">
-        <v>1</v>
-      </c>
-      <c r="O33" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="P33" s="9">
         <v>1</v>
